--- a/backend/preguntas.xlsx
+++ b/backend/preguntas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive - UNIVERSIDAD ALICANTE\Escritorio\plataformaopo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4244169E-694E-4A52-8EBA-6DEEC7A452B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E12AD3-EEC7-421E-B1EE-D8B5E3F60322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>tema_id</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Artículo 1.1 CE: España se constituye en un Estado social y democrático de Derecho, que propugna como valores superiores...</t>
+  </si>
+  <si>
+    <t>numero_test</t>
   </si>
 </sst>
 </file>
@@ -476,10 +479,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B276DA-A6DA-46D8-8C35-2A497CC075E5}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="55.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" customWidth="1"/>
     <col min="5" max="5" width="21.21875" customWidth="1"/>
     <col min="6" max="6" width="20.6640625" customWidth="1"/>
@@ -487,82 +490,147 @@
     <col min="8" max="8" width="60.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/backend/preguntas.xlsx
+++ b/backend/preguntas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive - UNIVERSIDAD ALICANTE\Escritorio\plataformaopo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E12AD3-EEC7-421E-B1EE-D8B5E3F60322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1567182-7D67-4A89-9AFE-633C0F2FAE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>tema_id</t>
   </si>
@@ -99,6 +99,21 @@
   </si>
   <si>
     <t>numero_test</t>
+  </si>
+  <si>
+    <t>La soberanía nacional reside en:</t>
+  </si>
+  <si>
+    <t>Las Cortes Generales</t>
+  </si>
+  <si>
+    <t>El pueblo español</t>
+  </si>
+  <si>
+    <t>El Gobierno</t>
+  </si>
+  <si>
+    <t>Artículo 1.2 CE: La soberanía nacional reside en el pueblo español, del que emanan los poderes del Estado.</t>
   </si>
 </sst>
 </file>
@@ -479,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B276DA-A6DA-46D8-8C35-2A497CC075E5}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -584,53 +599,26 @@
       <c r="B4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/backend/preguntas.xlsx
+++ b/backend/preguntas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive - UNIVERSIDAD ALICANTE\Escritorio\plataformaopo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1567182-7D67-4A89-9AFE-633C0F2FAE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A349F2-3A3F-438B-816C-675BB89A3D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>tema_id</t>
   </si>
@@ -114,6 +114,15 @@
   </si>
   <si>
     <t>Artículo 1.2 CE: La soberanía nacional reside en el pueblo español, del que emanan los poderes del Estado.</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -557,7 +566,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -586,7 +595,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>19</v>
@@ -615,7 +624,7 @@
         <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>25</v>

--- a/backend/preguntas.xlsx
+++ b/backend/preguntas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive - UNIVERSIDAD ALICANTE\Escritorio\plataformaopo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A349F2-3A3F-438B-816C-675BB89A3D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4CF9C9-FA96-408E-9B3C-FD6CEB3475D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
   <si>
     <t>tema_id</t>
   </si>
@@ -123,6 +123,114 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>La forma política del Estado español es:</t>
+  </si>
+  <si>
+    <t>La República federal</t>
+  </si>
+  <si>
+    <t>La Monarquía parlamentaria</t>
+  </si>
+  <si>
+    <t>La Monarquía constitucional</t>
+  </si>
+  <si>
+    <t>El Estado unitario</t>
+  </si>
+  <si>
+    <t>Artículo 1.3 CE: La forma política del Estado español es la Monarquía parlamentaria.</t>
+  </si>
+  <si>
+    <t>La capital del Estado es:</t>
+  </si>
+  <si>
+    <t>La ciudad de Madrid</t>
+  </si>
+  <si>
+    <t>La villa de Madrid</t>
+  </si>
+  <si>
+    <t>Madrid y sus provincias</t>
+  </si>
+  <si>
+    <t>El territorio nacional</t>
+  </si>
+  <si>
+    <t>Artículo 5 CE: La capital del Estado es la villa de Madrid.</t>
+  </si>
+  <si>
+    <t>Los españoles son mayores de edad a los:</t>
+  </si>
+  <si>
+    <t>16 años</t>
+  </si>
+  <si>
+    <t>18 años</t>
+  </si>
+  <si>
+    <t>21 años</t>
+  </si>
+  <si>
+    <t>19 años</t>
+  </si>
+  <si>
+    <t>Artículo 12 CE: Los españoles son mayores de edad a los dieciocho años.</t>
+  </si>
+  <si>
+    <t>¿Qué idioma es el oficial del Estado?</t>
+  </si>
+  <si>
+    <t>El español</t>
+  </si>
+  <si>
+    <t>El castellano</t>
+  </si>
+  <si>
+    <t>Las lenguas cooficiales</t>
+  </si>
+  <si>
+    <t>El castellano y el catalán</t>
+  </si>
+  <si>
+    <t>Artículo 3.1 CE: El castellano es la lengua española oficial del Estado.</t>
+  </si>
+  <si>
+    <t>La bandera de España está formada por tres franjas horizontales, roja, amarilla y roja, siendo la amarilla:</t>
+  </si>
+  <si>
+    <t>De igual anchura que cada una de las rojas</t>
+  </si>
+  <si>
+    <t>De doble anchura que cada una de las rojas</t>
+  </si>
+  <si>
+    <t>Del triple de anchura que las rojas</t>
+  </si>
+  <si>
+    <t>Proporcional al escudo</t>
+  </si>
+  <si>
+    <t>Artículo 4.1 CE sobre las proporciones de la bandera nacional.</t>
+  </si>
+  <si>
+    <t>Los partidos políticos expresan el pluralismo político, concurren a la formación de la voluntad popular y son instrumento fundamental para:</t>
+  </si>
+  <si>
+    <t>La participación política</t>
+  </si>
+  <si>
+    <t>La defensa del Estado</t>
+  </si>
+  <si>
+    <t>El control del Gobierno</t>
+  </si>
+  <si>
+    <t>El reparto de escaños</t>
+  </si>
+  <si>
+    <t>Artículo 6 CE que define la función de los partidos políticos.</t>
   </si>
 </sst>
 </file>
@@ -503,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B276DA-A6DA-46D8-8C35-2A497CC075E5}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -511,7 +619,7 @@
     <col min="5" max="5" width="21.21875" customWidth="1"/>
     <col min="6" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="18.44140625" customWidth="1"/>
-    <col min="8" max="8" width="60.77734375" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -630,6 +738,180 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/preguntas.xlsx
+++ b/backend/preguntas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive - UNIVERSIDAD ALICANTE\Escritorio\plataformaopo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4CF9C9-FA96-408E-9B3C-FD6CEB3475D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6D277D-559D-407B-93C9-6E8E35AB9F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
   <si>
     <t>tema_id</t>
   </si>
@@ -231,6 +231,42 @@
   </si>
   <si>
     <t>Artículo 6 CE que define la función de los partidos políticos.</t>
+  </si>
+  <si>
+    <t>La misión de las Fuerzas Armadas es:</t>
+  </si>
+  <si>
+    <t>Garantizar la soberanía, defender su integridad territorial y el ordenamiento constitucional</t>
+  </si>
+  <si>
+    <t>Proteger al Rey y a su familia</t>
+  </si>
+  <si>
+    <t>Mantener el orden público interior</t>
+  </si>
+  <si>
+    <t>Dirigir la política de defensa</t>
+  </si>
+  <si>
+    <t>Artículo 8.1 CE define la misión exacta de las Fuerzas Armadas.</t>
+  </si>
+  <si>
+    <t>¿Qué título de la CE está dedicado a los Derechos y Deberes fundamentales?</t>
+  </si>
+  <si>
+    <t>Título Preliminar</t>
+  </si>
+  <si>
+    <t>Título I</t>
+  </si>
+  <si>
+    <t>Título II</t>
+  </si>
+  <si>
+    <t>Título III</t>
+  </si>
+  <si>
+    <t>La estructura de la CE reserva el Título I para los derechos y deberes fundamentales.</t>
   </si>
 </sst>
 </file>
@@ -611,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B276DA-A6DA-46D8-8C35-2A497CC075E5}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -912,6 +948,136 @@
         <v>64</v>
       </c>
     </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/preguntas.xlsx
+++ b/backend/preguntas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive - UNIVERSIDAD ALICANTE\Escritorio\plataformaopo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6D277D-559D-407B-93C9-6E8E35AB9F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8191DA-DB0D-421F-B41B-01700C096D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{910E72EA-F883-4C38-9DE5-9CDCDBA3BD6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>tema_id</t>
   </si>
@@ -267,6 +267,51 @@
   </si>
   <si>
     <t>La estructura de la CE reserva el Título I para los derechos y deberes fundamentales.</t>
+  </si>
+  <si>
+    <t>¿Quién dirige la política interior y exterior, la Administración civil y militar y la defensa del Estado?</t>
+  </si>
+  <si>
+    <t>El Congreso de los Diputados</t>
+  </si>
+  <si>
+    <t>Artículo 97 de la CE: El Gobierno dirige la política interior y exterior...</t>
+  </si>
+  <si>
+    <t>¿Ante quién responde solidariamente el Gobierno en su gestión política?</t>
+  </si>
+  <si>
+    <t>Ante el Rey</t>
+  </si>
+  <si>
+    <t>Ante el Congreso de los Diputados</t>
+  </si>
+  <si>
+    <t>Ante las Cortes Generales</t>
+  </si>
+  <si>
+    <t>Ante el Tribunal Supremo</t>
+  </si>
+  <si>
+    <t>Artículo 108 de la CE establece la responsabilidad ante el Congreso.</t>
+  </si>
+  <si>
+    <t>El Gobierno se compone de:</t>
+  </si>
+  <si>
+    <t>El Presidente, el Rey y los Ministros</t>
+  </si>
+  <si>
+    <t>El Presidente, Vicepresidentes (en su caso) y Ministros</t>
+  </si>
+  <si>
+    <t>Solo de Ministros y Secretarios de Estado</t>
+  </si>
+  <si>
+    <t>Presidente y Tribunal Supremo</t>
+  </si>
+  <si>
+    <t>Artículo 98.1 CE detalla la composición del Gobierno.</t>
   </si>
 </sst>
 </file>
@@ -647,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B276DA-A6DA-46D8-8C35-2A497CC075E5}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -1013,6 +1058,27 @@
       <c r="B13">
         <v>2</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -1021,6 +1087,27 @@
       <c r="B14">
         <v>2</v>
       </c>
+      <c r="C14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -1029,53 +1116,26 @@
       <c r="B15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
+      <c r="C15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
